--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Трекер" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Трекер'!$A$1:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Трекер'!$A$1:$G$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -487,17 +487,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Распределить роли, выбрать платформу</t>
+          <t>Распределить роли, выбрать платформу, согласовать защиту вчетвером</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Все</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Свой HTML-сайт на GitHub Pages</t>
+          <t>Состав: 4 участницы</t>
         </is>
       </c>
     </row>
@@ -522,17 +522,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Структура учебника (оглавление), отправить преподавателю</t>
+          <t>Структура учебника (оглавление)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Имя1</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -557,17 +557,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Модуль 1: теория (план, суммы, разборы)</t>
+          <t>Введение и входной квиз (5 вопросов)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Имя1</t>
+          <t>Кеңес Маржан</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>module1.html</t>
+          <t>intro.html</t>
         </is>
       </c>
     </row>
@@ -592,17 +592,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Модуль 1: свои примеры (сумма над диагональю, сортировка выбором)</t>
+          <t>Модуль 1: план, суммы, MaxElement, UniqueElements, матрицы, зависимая граница, Binary</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Имя1</t>
+          <t>Кеңес Маржан</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -610,7 +610,11 @@
           <t>Готово</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>module1.html</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -623,17 +627,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Введение и входной квиз (5 вопросов)</t>
+          <t>Модуль 1: средний случай поиска, визуализации модуля 1, глоссарий</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Кеңес Маржан</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -641,11 +645,7 @@
           <t>Готово</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>intro.html</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -653,34 +653,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Промежуточная проверка модуля 1 у преподавателя</t>
+          <t>Модуль 1: свои примеры (сумма над диагональю, сортировка выбором), типичные ошибки</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Имя1</t>
+          <t>Алтыбаева Аружан</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Уточнить</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Записать замечания преподавателя</t>
-        </is>
-      </c>
+          <t>Готово</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -688,32 +684,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>8-10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Модуль 2: теория (рекуррентности, обратные подстановки, индукция)</t>
+          <t>Промежуточная проверка модуля 1 у преподавателя</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Имя3</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>Уточнить</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>module2.html</t>
+          <t>Записать замечания, если были</t>
         </is>
       </c>
     </row>
@@ -728,17 +724,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Модуль 2: Ханойская башня и интерактивная модель</t>
+          <t>Модуль 2: план, рекуррентности, обратные подстановки, индукция, факториал</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Имя3</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -748,7 +744,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>assets/viz/hanoi.js</t>
+          <t>module2.html</t>
         </is>
       </c>
     </row>
@@ -763,17 +759,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Модуль 2: Фибоначчи, мемоизация, стек, хвостовая рекурсия</t>
+          <t>Модуль 2: Ханойская башня — теория, дерево, интерактивная модель</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -781,7 +777,11 @@
           <t>Готово</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>assets/viz/hanoi.js</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -794,17 +794,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Модуль 2: свои примеры (MaxDC, Power, рекурсивная сумма)</t>
+          <t>Модуль 2: BinRec, правило гладкости, Фибоначчи, мемоизация, стек, хвостовая рекурсия</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Абильмажитова Алина</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -825,17 +825,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Квизы модулей 1 и 2 (по 10 вопросов, объяснения к вариантам)</t>
+          <t>Модуль 2: свои примеры (рекурсивная сумма, MaxDC, Power), визуализации</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Абильмажитова Алина</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>data/quizzes.js</t>
+          <t>assets/viz/module2.js</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Задачи модуля 1 (A4, B4, C2, Ф2, Э1)</t>
+          <t>Квиз модуля 1 и 13 задач модуля 1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Имя1</t>
+          <t>Алтыбаева Аружан</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Задачи модуля 2 (A4, B4, C2, Ф2, Э1)</t>
+          <t>Квиз модуля 2 и задачи модуля 2 A1, A2, A4, B3, B4, C1, C2, Ф2, Э1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Имя3</t>
+          <t>Абильмажитова Алина</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -930,17 +930,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Визуализации модуля 1 (сетка пар, цикл i←2i, график роста, средний случай)</t>
+          <t>Задачи модуля 2 A3, B1, B2, Ф1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Имя1</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -948,11 +948,7 @@
           <t>Готово</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>assets/viz/module1.js</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -965,17 +961,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Python: скрипты со счётчиками и графики</t>
+          <t>Python: скрипты со счётчиками, графики, verify_answers.py</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Алтыбаева Аружан</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -985,7 +981,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>code/, run_all.py</t>
+          <t>code/</t>
         </is>
       </c>
     </row>
@@ -1000,17 +996,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Python: verify_answers.py — проверка всех ответов</t>
+          <t>Английская версия сайта</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1020,7 +1016,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66 проверок пройдено</t>
+          <t>en/, data/en/</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1031,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Перекрёстная проверка: Имя1 проверяет модуль 2</t>
+          <t>Ручная проверка: задачи модуля 1 (все 13)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Имя1</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1055,7 +1051,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Проверить каждое решение вручную</t>
+          <t>Список — в руководстве команды</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1066,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Перекрёстная проверка: Имя3 проверяет модуль 1</t>
+          <t>Ручная проверка: модуль 2, часть Алины (A1, A2, A4, B3, B4, C1, C2, Ф2, Э1)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Имя3</t>
+          <t>Кеңес Маржан</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1090,7 +1086,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Проверить каждое решение вручную</t>
+          <t>C1, C2 — доказательства полностью</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1101,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Перекрёстная проверка: Имя2 проверяет введение, квизы, глоссарий</t>
+          <t>Ручная проверка: теория модуля 1, все квизы, все подсказки</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Абильмажитова Алина</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1136,12 +1132,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Тест учебника на 1–2 бакалаврах, записать отзывы</t>
+          <t>Ручная проверка: Ханой, задачи модуля 2 A3, B1, B2, Ф1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Все</t>
+          <t>Алтыбаева Аружан</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1151,14 +1147,10 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Раздел 6 отчёта</t>
-        </is>
-      </c>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1166,17 +1158,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Исправления по отзывам и проверке</t>
+          <t>Тест на бакалавре (Саян, 2 курс), запись отзыва</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Все</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1186,10 +1178,14 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Не начато</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>В работе</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Подтвердить формулировки с Саяном</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1202,12 +1198,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Отчёт report.md / report.docx: роли, вклад, ИИ, отзывы</t>
+          <t>Исправления по отзыву бакалавра</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Имя3</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1217,12 +1213,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Заполнить места _заполнить_</t>
+          <t>Таблица O/Ω/Θ, легенда дерева Ханоя, памятка к задачам</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1233,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Публикация на GitHub Pages, проверка ссылки</t>
+          <t>Отчёт report.md / report.docx</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Имя2</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1255,7 +1251,11 @@
           <t>Готово</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Проверить проценты вклада</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Презентация и репетиция защиты (defense_outline.md)</t>
+          <t>Трекер задач</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Все</t>
+          <t>Алтыбаева Аружан</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Не начато</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5 задач у доски, включая Ханой</t>
+          <t>tracker.xlsx</t>
         </is>
       </c>
     </row>
@@ -1298,35 +1298,70 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Репетиция защиты (10 минут, 4 части)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>defense_outline.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Защита</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Все</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G26"/>
+  <autoFilter ref="A1:G27"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,В работе,Готово,Уточнить"</formula1>
     </dataValidation>
   </dataValidations>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Трекер" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Трекер'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Трекер'!$A$1:$G$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>8-10</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ручная проверка: задачи модуля 1 (все 13)</t>
+          <t>Казахская версия сайта</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Список — в руководстве команды</t>
+          <t>kk/, data/kk/, assets/i18n-kk.js</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ручная проверка: модуль 2, часть Алины (A1, A2, A4, B3, B4, C1, C2, Ф2, Э1)</t>
+          <t>Ручная проверка: задачи модуля 1 (все 13)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Кеңес Маржан</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>C1, C2 — доказательства полностью</t>
+          <t>Список — в руководстве команды</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Ручная проверка: теория модуля 1, все квизы, все подсказки</t>
+          <t>Ручная проверка: модуль 2, часть Алины (A1, A2, A4, B3, B4, C1, C2, Ф2, Э1)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Абильмажитова Алина</t>
+          <t>Кеңес Маржан</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1119,7 +1119,11 @@
           <t>В работе</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>C1, C2 — доказательства полностью</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1132,12 +1136,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ручная проверка: Ханой, задачи модуля 2 A3, B1, B2, Ф1</t>
+          <t>Ручная проверка: теория модуля 1, все квизы, все подсказки</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Алтыбаева Аружан</t>
+          <t>Абильмажитова Алина</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1163,12 +1167,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Тест на бакалавре (Саян, 2 курс), запись отзыва</t>
+          <t>Ручная проверка: Ханой, задачи модуля 2 A3, B1, B2, Ф1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Калжан Ақниет</t>
+          <t>Алтыбаева Аружан</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1181,11 +1185,7 @@
           <t>В работе</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Подтвердить формулировки с Саяном</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Исправления по отзыву бакалавра</t>
+          <t>Тест на бакалавре (Саян, 2 курс), запись отзыва</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Готово</t>
+          <t>В работе</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Таблица O/Ω/Θ, легенда дерева Ханоя, памятка к задачам</t>
+          <t>Подтвердить формулировки с Саяном</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Отчёт report.md / report.docx</t>
+          <t>Исправления по отзыву бакалавра</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Проверить проценты вклада</t>
+          <t>Таблица O/Ω/Θ, легенда дерева Ханоя, памятка к задачам</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Трекер задач</t>
+          <t>Отчёт report.md / report.docx</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Алтыбаева Аружан</t>
+          <t>Калжан Ақниет</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>tracker.xlsx</t>
+          <t>Проверить проценты вклада</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Репетиция защиты (10 минут, 4 части)</t>
+          <t>Трекер задач</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Все</t>
+          <t>Алтыбаева Аружан</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Не начато</t>
+          <t>Готово</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>defense_outline.md</t>
+          <t>tracker.xlsx</t>
         </is>
       </c>
     </row>
@@ -1333,35 +1333,70 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Репетиция защиты (10 минут, 4 части)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Все</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Не начато</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>defense_outline.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Защита</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Все</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Не начато</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G27"/>
+  <autoFilter ref="A1:G28"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Не начато,В работе,Готово,Уточнить"</formula1>
     </dataValidation>
   </dataValidations>
